--- a/Script_9_region_cell_type_enrichment_with_scRNAseq/region protein marker in scRNAseq cell type/region_specific_upregulated_proteins.xlsx
+++ b/Script_9_region_cell_type_enrichment_with_scRNAseq/region protein marker in scRNAseq cell type/region_specific_upregulated_proteins.xlsx
@@ -358,26 +358,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Gene.symbol</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Uniprot.ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>p.value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>FDR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Log2FC</t>
         </is>
@@ -4601,26 +4606,31 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Gene.symbol</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Uniprot.ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>p.value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>FDR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Log2FC</t>
         </is>
